--- a/database/event/6793/event_6793_evp_summary.xlsx
+++ b/database/event/6793/event_6793_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>9.1945</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>4.976</v>
       </c>
       <c r="D2" t="n">
         <v>3.293</v>
@@ -545,7 +545,7 @@
         <v>9.1586</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4.9566</v>
       </c>
       <c r="D3" t="n">
         <v>3.2785</v>
@@ -591,7 +591,7 @@
         <v>5.5763</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3.0179</v>
       </c>
       <c r="D4" t="n">
         <v>1.8313</v>
@@ -637,7 +637,7 @@
         <v>5.1071</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.7639</v>
       </c>
       <c r="D5" t="n">
         <v>1.6418</v>
@@ -683,7 +683,7 @@
         <v>4.7822</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.5881</v>
       </c>
       <c r="D6" t="n">
         <v>1.5105</v>
@@ -729,7 +729,7 @@
         <v>4.7736</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.5834</v>
       </c>
       <c r="D7" t="n">
         <v>1.5071</v>
@@ -775,7 +775,7 @@
         <v>4.3504</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.3544</v>
       </c>
       <c r="D8" t="n">
         <v>1.3361</v>
@@ -821,7 +821,7 @@
         <v>3.8322</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.074</v>
       </c>
       <c r="D9" t="n">
         <v>1.1268</v>
@@ -867,7 +867,7 @@
         <v>3.6814</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1.9923</v>
       </c>
       <c r="D10" t="n">
         <v>1.0658</v>
@@ -913,7 +913,7 @@
         <v>3.3972</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.8385</v>
       </c>
       <c r="D11" t="n">
         <v>0.951</v>
@@ -959,7 +959,7 @@
         <v>3.0128</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.6305</v>
       </c>
       <c r="D12" t="n">
         <v>0.7957</v>
@@ -1005,7 +1005,7 @@
         <v>2.7703</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.4993</v>
       </c>
       <c r="D13" t="n">
         <v>0.6978</v>
@@ -1051,7 +1051,7 @@
         <v>2.7323</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.4787</v>
       </c>
       <c r="D14" t="n">
         <v>0.6824</v>
@@ -1097,7 +1097,7 @@
         <v>2.7269</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.4758</v>
       </c>
       <c r="D15" t="n">
         <v>0.6802</v>
@@ -1143,7 +1143,7 @@
         <v>2.5452</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.3774</v>
       </c>
       <c r="D16" t="n">
         <v>0.6068</v>
@@ -1189,7 +1189,7 @@
         <v>2.3262</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="D17" t="n">
         <v>0.5184</v>
@@ -1235,7 +1235,7 @@
         <v>2.1361</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.156</v>
       </c>
       <c r="D18" t="n">
         <v>0.4416</v>
@@ -1281,7 +1281,7 @@
         <v>2.1338</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.1548</v>
       </c>
       <c r="D19" t="n">
         <v>0.4406</v>
@@ -1327,7 +1327,7 @@
         <v>2.1269</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.1511</v>
       </c>
       <c r="D20" t="n">
         <v>0.4379</v>
@@ -1373,7 +1373,7 @@
         <v>2.011</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.0883</v>
       </c>
       <c r="D21" t="n">
         <v>0.391</v>
@@ -1419,7 +1419,7 @@
         <v>2.0032</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.0841</v>
       </c>
       <c r="D22" t="n">
         <v>0.3879</v>
@@ -1465,7 +1465,7 @@
         <v>1.9323</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.0457</v>
       </c>
       <c r="D23" t="n">
         <v>0.3592</v>
@@ -1511,7 +1511,7 @@
         <v>1.8966</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.0264</v>
       </c>
       <c r="D24" t="n">
         <v>0.3448</v>
@@ -1557,7 +1557,7 @@
         <v>1.888</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.0218</v>
       </c>
       <c r="D25" t="n">
         <v>0.3413</v>
@@ -1603,7 +1603,7 @@
         <v>1.8535</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.0031</v>
       </c>
       <c r="D26" t="n">
         <v>0.3274</v>
@@ -1649,7 +1649,7 @@
         <v>1.7764</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.9614</v>
       </c>
       <c r="D27" t="n">
         <v>0.2963</v>
@@ -1695,7 +1695,7 @@
         <v>1.6826</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.9106</v>
       </c>
       <c r="D28" t="n">
         <v>0.2584</v>
@@ -1741,7 +1741,7 @@
         <v>1.656</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.8962</v>
       </c>
       <c r="D29" t="n">
         <v>0.2476</v>
@@ -1787,7 +1787,7 @@
         <v>1.6425</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.8889</v>
       </c>
       <c r="D30" t="n">
         <v>0.2422</v>
@@ -1833,7 +1833,7 @@
         <v>1.6199</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.8767</v>
       </c>
       <c r="D31" t="n">
         <v>0.233</v>
@@ -1879,7 +1879,7 @@
         <v>1.5886</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.8597</v>
       </c>
       <c r="D32" t="n">
         <v>0.2204</v>
@@ -1925,7 +1925,7 @@
         <v>1.5725</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.851</v>
       </c>
       <c r="D33" t="n">
         <v>0.2139</v>
@@ -1971,7 +1971,7 @@
         <v>1.5077</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="D34" t="n">
         <v>0.1877</v>
@@ -2017,7 +2017,7 @@
         <v>1.4814</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.8017</v>
       </c>
       <c r="D35" t="n">
         <v>0.1771</v>
@@ -2063,7 +2063,7 @@
         <v>1.4782</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D36" t="n">
         <v>0.1758</v>
@@ -2109,7 +2109,7 @@
         <v>1.4153</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.7659</v>
       </c>
       <c r="D37" t="n">
         <v>0.1504</v>
@@ -2155,7 +2155,7 @@
         <v>1.3077</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.7077</v>
       </c>
       <c r="D38" t="n">
         <v>0.1069</v>
@@ -2201,7 +2201,7 @@
         <v>1.0739</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.5812</v>
       </c>
       <c r="D39" t="n">
         <v>0.0125</v>
@@ -2247,7 +2247,7 @@
         <v>1.0371</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.5613</v>
       </c>
       <c r="D40" t="n">
         <v>-0.0024</v>
@@ -2293,7 +2293,7 @@
         <v>0.98</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.5304</v>
       </c>
       <c r="D41" t="n">
         <v>-0.0255</v>
@@ -2339,7 +2339,7 @@
         <v>0.9796</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.5302</v>
       </c>
       <c r="D42" t="n">
         <v>-0.0256</v>
@@ -2385,7 +2385,7 @@
         <v>0.87</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.4708</v>
       </c>
       <c r="D43" t="n">
         <v>-0.0699</v>
@@ -2431,7 +2431,7 @@
         <v>0.8516</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.4609</v>
       </c>
       <c r="D44" t="n">
         <v>-0.07729999999999999</v>
@@ -2477,7 +2477,7 @@
         <v>0.8254</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.4467</v>
       </c>
       <c r="D45" t="n">
         <v>-0.08790000000000001</v>
@@ -2523,7 +2523,7 @@
         <v>0.62</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.3355</v>
       </c>
       <c r="D46" t="n">
         <v>-0.1709</v>
@@ -2569,7 +2569,7 @@
         <v>0.6119</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.3312</v>
       </c>
       <c r="D47" t="n">
         <v>-0.1742</v>
@@ -2615,7 +2615,7 @@
         <v>0.5397</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.2921</v>
       </c>
       <c r="D48" t="n">
         <v>-0.2033</v>
@@ -2661,7 +2661,7 @@
         <v>0.5109</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.2765</v>
       </c>
       <c r="D49" t="n">
         <v>-0.215</v>
@@ -2707,7 +2707,7 @@
         <v>0.4503</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.2437</v>
       </c>
       <c r="D50" t="n">
         <v>-0.2395</v>
@@ -2753,7 +2753,7 @@
         <v>0.3831</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.2073</v>
       </c>
       <c r="D51" t="n">
         <v>-0.2666</v>
@@ -2799,7 +2799,7 @@
         <v>0.3768</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.2039</v>
       </c>
       <c r="D52" t="n">
         <v>-0.2691</v>
@@ -2845,7 +2845,7 @@
         <v>0.1348</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.073</v>
       </c>
       <c r="D53" t="n">
         <v>-0.3669</v>
@@ -2891,7 +2891,7 @@
         <v>0.122</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="D54" t="n">
         <v>-0.3721</v>
@@ -2937,7 +2937,7 @@
         <v>0.104</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.0563</v>
       </c>
       <c r="D55" t="n">
         <v>-0.3793</v>
@@ -2983,7 +2983,7 @@
         <v>0.08459999999999999</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>0.0458</v>
       </c>
       <c r="D56" t="n">
         <v>-0.3872</v>
@@ -3029,7 +3029,7 @@
         <v>0.0371</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>0.0201</v>
       </c>
       <c r="D57" t="n">
         <v>-0.4064</v>
@@ -3075,7 +3075,7 @@
         <v>0.0336</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>0.0182</v>
       </c>
       <c r="D58" t="n">
         <v>-0.4078</v>
@@ -3121,7 +3121,7 @@
         <v>-0.4078</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.2207</v>
       </c>
       <c r="D59" t="n">
         <v>-0.5861</v>
@@ -3167,7 +3167,7 @@
         <v>-0.5027</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.2721</v>
       </c>
       <c r="D60" t="n">
         <v>-0.6244</v>
@@ -3213,7 +3213,7 @@
         <v>-0.5834</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.3157</v>
       </c>
       <c r="D61" t="n">
         <v>-0.657</v>
@@ -3259,7 +3259,7 @@
         <v>-0.6465</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.3499</v>
       </c>
       <c r="D62" t="n">
         <v>-0.6825</v>
@@ -3305,7 +3305,7 @@
         <v>-0.9032</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.4888</v>
       </c>
       <c r="D63" t="n">
         <v>-0.7862</v>
@@ -3351,7 +3351,7 @@
         <v>-0.9056</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.4901</v>
       </c>
       <c r="D64" t="n">
         <v>-0.7872</v>
@@ -3397,7 +3397,7 @@
         <v>-0.96</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.5195</v>
       </c>
       <c r="D65" t="n">
         <v>-0.8092</v>
@@ -3443,7 +3443,7 @@
         <v>-1.0089</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.546</v>
       </c>
       <c r="D66" t="n">
         <v>-0.8289</v>
@@ -3489,7 +3489,7 @@
         <v>-1.0273</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.556</v>
       </c>
       <c r="D67" t="n">
         <v>-0.8364</v>
@@ -3535,7 +3535,7 @@
         <v>-1.1552</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.6252</v>
       </c>
       <c r="D68" t="n">
         <v>-0.888</v>
@@ -3581,7 +3581,7 @@
         <v>-1.2136</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="D69" t="n">
         <v>-0.9116</v>
@@ -3627,7 +3627,7 @@
         <v>-1.2463</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.6745</v>
       </c>
       <c r="D70" t="n">
         <v>-0.9248</v>
@@ -3673,7 +3673,7 @@
         <v>-1.3903</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.7524</v>
       </c>
       <c r="D71" t="n">
         <v>-0.983</v>
@@ -3719,7 +3719,7 @@
         <v>-1.4252</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.7713</v>
       </c>
       <c r="D72" t="n">
         <v>-0.9971</v>
@@ -3765,7 +3765,7 @@
         <v>-1.5409</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.8339</v>
       </c>
       <c r="D73" t="n">
         <v>-1.0439</v>
@@ -3811,7 +3811,7 @@
         <v>-1.6207</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.8771</v>
       </c>
       <c r="D74" t="n">
         <v>-1.0761</v>
@@ -3857,7 +3857,7 @@
         <v>-1.7981</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.9731</v>
       </c>
       <c r="D75" t="n">
         <v>-1.1478</v>
@@ -3903,7 +3903,7 @@
         <v>-1.902</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.0293</v>
       </c>
       <c r="D76" t="n">
         <v>-1.1897</v>
@@ -3949,7 +3949,7 @@
         <v>-1.9086</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.0329</v>
       </c>
       <c r="D77" t="n">
         <v>-1.1924</v>
@@ -3995,7 +3995,7 @@
         <v>-2.0339</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.1007</v>
       </c>
       <c r="D78" t="n">
         <v>-1.243</v>
@@ -4041,7 +4041,7 @@
         <v>-2.0601</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.1149</v>
       </c>
       <c r="D79" t="n">
         <v>-1.2536</v>
@@ -4087,7 +4087,7 @@
         <v>-3.4295</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-1.856</v>
       </c>
       <c r="D80" t="n">
         <v>-1.8068</v>
@@ -4133,7 +4133,7 @@
         <v>-4.4975</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-2.434</v>
       </c>
       <c r="D81" t="n">
         <v>-2.2383</v>

--- a/database/event/6793/event_6793_evp_summary.xlsx
+++ b/database/event/6793/event_6793_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.1945</v>
+        <v>9.8857</v>
       </c>
       <c r="C2" t="n">
-        <v>4.976</v>
+        <v>5.3501</v>
       </c>
       <c r="D2" t="n">
-        <v>3.293</v>
+        <v>3.4946</v>
       </c>
       <c r="E2" t="n">
-        <v>9.1945</v>
+        <v>9.8857</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1782</v>
+        <v>3.8693</v>
       </c>
       <c r="G2" t="n">
         <v>6.0163</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1782</v>
+        <v>3.8693</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1782</v>
+        <v>3.8693</v>
       </c>
       <c r="J2" t="n">
         <v>6.0163</v>
@@ -529,7 +529,7 @@
         <v>164</v>
       </c>
       <c r="M2" t="n">
-        <v>9.1945</v>
+        <v>9.8856</v>
       </c>
       <c r="N2" t="n">
         <v>277</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.1586</v>
+        <v>9.4999</v>
       </c>
       <c r="C3" t="n">
-        <v>4.9566</v>
+        <v>5.1413</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2785</v>
+        <v>3.3409</v>
       </c>
       <c r="E3" t="n">
-        <v>9.1586</v>
+        <v>9.4999</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7368</v>
+        <v>4.0782</v>
       </c>
       <c r="G3" t="n">
         <v>5.4217</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7368</v>
+        <v>4.0915</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7368</v>
+        <v>4.0915</v>
       </c>
       <c r="J3" t="n">
         <v>5.4217</v>
@@ -575,7 +575,7 @@
         <v>177</v>
       </c>
       <c r="M3" t="n">
-        <v>9.1585</v>
+        <v>9.513200000000001</v>
       </c>
       <c r="N3" t="n">
         <v>306</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5763</v>
+        <v>6.0359</v>
       </c>
       <c r="C4" t="n">
-        <v>3.0179</v>
+        <v>3.2666</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8313</v>
+        <v>1.9608</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5763</v>
+        <v>6.0359</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9872</v>
+        <v>2.4468</v>
       </c>
       <c r="G4" t="n">
         <v>3.5891</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9872</v>
+        <v>2.4468</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9872</v>
+        <v>2.4468</v>
       </c>
       <c r="J4" t="n">
         <v>3.5891</v>
@@ -621,7 +621,7 @@
         <v>164</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5763</v>
+        <v>6.0359</v>
       </c>
       <c r="N4" t="n">
         <v>277</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1071</v>
+        <v>5.0802</v>
       </c>
       <c r="C5" t="n">
-        <v>2.7639</v>
+        <v>2.7494</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6418</v>
+        <v>1.58</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1071</v>
+        <v>5.0802</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6148</v>
+        <v>3.5879</v>
       </c>
       <c r="G5" t="n">
         <v>1.4923</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6148</v>
+        <v>3.5879</v>
       </c>
       <c r="I5" t="n">
         <v>3.6486</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7822</v>
+        <v>4.9508</v>
       </c>
       <c r="C6" t="n">
-        <v>2.5881</v>
+        <v>2.6793</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5105</v>
+        <v>1.5285</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7822</v>
+        <v>4.9508</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9678</v>
+        <v>2.8619</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1856</v>
+        <v>2.0889</v>
       </c>
       <c r="H6" t="n">
-        <v>5.4865</v>
+        <v>2.8619</v>
       </c>
       <c r="I6" t="n">
-        <v>5.5377</v>
+        <v>2.8619</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1856</v>
+        <v>2.0889</v>
       </c>
       <c r="K6" t="n">
-        <v>277</v>
+        <v>131</v>
       </c>
       <c r="L6" t="n">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="M6" t="n">
-        <v>5.3521</v>
+        <v>4.9508</v>
       </c>
       <c r="N6" t="n">
-        <v>357</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.7736</v>
+        <v>4.7562</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5834</v>
+        <v>2.574</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5071</v>
+        <v>1.451</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7736</v>
+        <v>4.7562</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6847</v>
+        <v>4.9418</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0889</v>
+        <v>-0.1856</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6847</v>
+        <v>5.4456</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6847</v>
+        <v>5.5377</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0889</v>
+        <v>-0.1856</v>
       </c>
       <c r="K7" t="n">
-        <v>131</v>
+        <v>277</v>
       </c>
       <c r="L7" t="n">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7736</v>
+        <v>5.3521</v>
       </c>
       <c r="N7" t="n">
-        <v>292</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8">
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3504</v>
+        <v>4.7012</v>
       </c>
       <c r="C8" t="n">
-        <v>2.3544</v>
+        <v>2.5443</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3361</v>
+        <v>1.429</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3504</v>
+        <v>4.7012</v>
       </c>
       <c r="F8" t="n">
-        <v>4.1462</v>
+        <v>4.497</v>
       </c>
       <c r="G8" t="n">
         <v>0.2042</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1982</v>
+        <v>4.7483</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2177</v>
+        <v>4.7882</v>
       </c>
       <c r="J8" t="n">
         <v>0.2042</v>
@@ -805,7 +805,7 @@
         <v>53</v>
       </c>
       <c r="M8" t="n">
-        <v>4.4219</v>
+        <v>4.9924</v>
       </c>
       <c r="N8" t="n">
         <v>245</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.8322</v>
+        <v>4.5573</v>
       </c>
       <c r="C9" t="n">
-        <v>2.074</v>
+        <v>2.4664</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1268</v>
+        <v>1.3717</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8322</v>
+        <v>4.5573</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7183</v>
+        <v>2.4434</v>
       </c>
       <c r="G9" t="n">
         <v>2.1139</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7183</v>
+        <v>2.4434</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7183</v>
+        <v>2.4434</v>
       </c>
       <c r="J9" t="n">
         <v>2.1139</v>
@@ -851,7 +851,7 @@
         <v>161</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8322</v>
+        <v>4.5573</v>
       </c>
       <c r="N9" t="n">
         <v>292</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6814</v>
+        <v>3.7411</v>
       </c>
       <c r="C10" t="n">
-        <v>1.9923</v>
+        <v>2.0247</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0658</v>
+        <v>1.0465</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6814</v>
+        <v>3.7411</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0308</v>
+        <v>2.0905</v>
       </c>
       <c r="G10" t="n">
         <v>1.6506</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0308</v>
+        <v>2.0905</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0308</v>
+        <v>2.0905</v>
       </c>
       <c r="J10" t="n">
         <v>1.6506</v>
@@ -897,7 +897,7 @@
         <v>177</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6814</v>
+        <v>3.7411</v>
       </c>
       <c r="N10" t="n">
         <v>306</v>
@@ -906,185 +906,185 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3972</v>
+        <v>3.645</v>
       </c>
       <c r="C11" t="n">
-        <v>1.8385</v>
+        <v>1.9726</v>
       </c>
       <c r="D11" t="n">
-        <v>0.951</v>
+        <v>1.0083</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3972</v>
+        <v>3.645</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0783</v>
+        <v>3.0343</v>
       </c>
       <c r="G11" t="n">
-        <v>2.3189</v>
+        <v>0.6107</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0783</v>
+        <v>3.0343</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0783</v>
+        <v>3.0598</v>
       </c>
       <c r="J11" t="n">
-        <v>2.3189</v>
+        <v>0.6107</v>
       </c>
       <c r="K11" t="n">
-        <v>113</v>
+        <v>192</v>
       </c>
       <c r="L11" t="n">
-        <v>164</v>
+        <v>53</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3972</v>
+        <v>3.6705</v>
       </c>
       <c r="N11" t="n">
-        <v>277</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BOROS</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0128</v>
+        <v>3.4204</v>
       </c>
       <c r="C12" t="n">
-        <v>1.6305</v>
+        <v>1.8511</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7957</v>
+        <v>0.9188</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0128</v>
+        <v>3.4204</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1658</v>
+        <v>1.1015</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.153</v>
+        <v>2.3189</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1658</v>
+        <v>1.1015</v>
       </c>
       <c r="I12" t="n">
-        <v>3.1658</v>
+        <v>1.1015</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.153</v>
+        <v>2.3189</v>
       </c>
       <c r="K12" t="n">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="L12" t="n">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0128</v>
+        <v>3.4204</v>
       </c>
       <c r="N12" t="n">
-        <v>205</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>headtr1ck</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7703</v>
+        <v>3.2938</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4993</v>
+        <v>1.7826</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6978</v>
+        <v>0.8683</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7703</v>
+        <v>3.2938</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7703</v>
+        <v>3.2938</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7703</v>
+        <v>3.2938</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7703</v>
+        <v>3.2938</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>196</v>
+        <v>253</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7703</v>
+        <v>3.2938</v>
       </c>
       <c r="N13" t="n">
-        <v>196</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7323</v>
+        <v>3.142</v>
       </c>
       <c r="C14" t="n">
-        <v>1.4787</v>
+        <v>1.7004</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6824</v>
+        <v>0.8079</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7323</v>
+        <v>3.142</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1216</v>
+        <v>3.6161</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6107</v>
+        <v>-0.4741</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1216</v>
+        <v>3.6161</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1314</v>
+        <v>3.6161</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6107</v>
+        <v>-0.4741</v>
       </c>
       <c r="K14" t="n">
         <v>192</v>
       </c>
       <c r="L14" t="n">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7421</v>
+        <v>3.142</v>
       </c>
       <c r="N14" t="n">
-        <v>245</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.7269</v>
+        <v>3.0829</v>
       </c>
       <c r="C15" t="n">
-        <v>1.4758</v>
+        <v>1.6684</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6802</v>
+        <v>0.7843</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7269</v>
+        <v>3.0829</v>
       </c>
       <c r="F15" t="n">
-        <v>2.14</v>
+        <v>2.496</v>
       </c>
       <c r="G15" t="n">
         <v>0.5869</v>
       </c>
       <c r="H15" t="n">
-        <v>2.14</v>
+        <v>2.496</v>
       </c>
       <c r="I15" t="n">
-        <v>2.14</v>
+        <v>2.496</v>
       </c>
       <c r="J15" t="n">
         <v>0.5869</v>
@@ -1127,7 +1127,7 @@
         <v>55</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7269</v>
+        <v>3.0829</v>
       </c>
       <c r="N15" t="n">
         <v>265</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>headtr1ck</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5452</v>
+        <v>3.0687</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3774</v>
+        <v>1.6608</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6068</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5452</v>
+        <v>3.0687</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5452</v>
+        <v>3.0687</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5452</v>
+        <v>3.0687</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5452</v>
+        <v>3.0687</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>253</v>
+        <v>196</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.5452</v>
+        <v>3.0687</v>
       </c>
       <c r="N16" t="n">
-        <v>253</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nawwk</t>
+          <t>BOROS</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3262</v>
+        <v>3.0484</v>
       </c>
       <c r="C17" t="n">
-        <v>1.2589</v>
+        <v>1.6498</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5184</v>
+        <v>0.7706</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3262</v>
+        <v>3.0484</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3062</v>
+        <v>3.2014</v>
       </c>
       <c r="G17" t="n">
-        <v>2.02</v>
+        <v>-0.153</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3062</v>
+        <v>3.2014</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3062</v>
+        <v>3.2014</v>
       </c>
       <c r="J17" t="n">
-        <v>2.02</v>
+        <v>-0.153</v>
       </c>
       <c r="K17" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="L17" t="n">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3262</v>
+        <v>3.0484</v>
       </c>
       <c r="N17" t="n">
-        <v>303</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1361</v>
+        <v>2.7852</v>
       </c>
       <c r="C18" t="n">
-        <v>1.156</v>
+        <v>1.5073</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4416</v>
+        <v>0.6657</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1361</v>
+        <v>2.7852</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3866</v>
+        <v>3.0357</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2505</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3866</v>
+        <v>3.0357</v>
       </c>
       <c r="I18" t="n">
-        <v>2.3866</v>
+        <v>3.0357</v>
       </c>
       <c r="J18" t="n">
         <v>-0.2505</v>
@@ -1265,7 +1265,7 @@
         <v>55</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1361</v>
+        <v>2.7852</v>
       </c>
       <c r="N18" t="n">
         <v>265</v>
@@ -1274,219 +1274,219 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>nawwk</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1338</v>
+        <v>2.3262</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1548</v>
+        <v>1.2589</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4406</v>
+        <v>0.4828</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1338</v>
+        <v>2.3262</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1338</v>
+        <v>0.3062</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1338</v>
+        <v>0.3062</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1338</v>
+        <v>0.3062</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="K19" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="M19" t="n">
-        <v>2.1338</v>
+        <v>2.3262</v>
       </c>
       <c r="N19" t="n">
-        <v>196</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1269</v>
+        <v>2.3001</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1511</v>
+        <v>1.2448</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4379</v>
+        <v>0.4724</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1269</v>
+        <v>2.3001</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3761</v>
+        <v>1.2391</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7508</v>
+        <v>1.061</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3761</v>
+        <v>1.2391</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3761</v>
+        <v>1.2391</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7508</v>
+        <v>1.061</v>
       </c>
       <c r="K20" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="L20" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="M20" t="n">
-        <v>2.1269</v>
+        <v>2.3001</v>
       </c>
       <c r="N20" t="n">
-        <v>277</v>
+        <v>306</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.011</v>
+        <v>2.2506</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0883</v>
+        <v>1.218</v>
       </c>
       <c r="D21" t="n">
-        <v>0.391</v>
+        <v>0.4527</v>
       </c>
       <c r="E21" t="n">
-        <v>2.011</v>
+        <v>2.2506</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4851</v>
+        <v>2.2506</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4741</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.4851</v>
+        <v>2.2506</v>
       </c>
       <c r="I21" t="n">
-        <v>2.4851</v>
+        <v>2.2506</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4741</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L21" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.011</v>
+        <v>2.2506</v>
       </c>
       <c r="N21" t="n">
-        <v>303</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.0032</v>
+        <v>2.1269</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0841</v>
+        <v>1.1511</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3879</v>
+        <v>0.4034</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0032</v>
+        <v>2.1269</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5938</v>
+        <v>1.3761</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4094</v>
+        <v>0.7508</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5938</v>
+        <v>1.3761</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5938</v>
+        <v>1.3761</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4094</v>
+        <v>0.7508</v>
       </c>
       <c r="K22" t="n">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="L22" t="n">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="M22" t="n">
-        <v>2.0032</v>
+        <v>2.1269</v>
       </c>
       <c r="N22" t="n">
-        <v>306</v>
+        <v>277</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.9323</v>
+        <v>2.01</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0457</v>
+        <v>1.0878</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3592</v>
+        <v>0.3569</v>
       </c>
       <c r="E23" t="n">
-        <v>1.9323</v>
+        <v>2.01</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8713</v>
+        <v>1.6006</v>
       </c>
       <c r="G23" t="n">
-        <v>1.061</v>
+        <v>0.4094</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8713</v>
+        <v>1.6006</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8713</v>
+        <v>1.6006</v>
       </c>
       <c r="J23" t="n">
-        <v>1.061</v>
+        <v>0.4094</v>
       </c>
       <c r="K23" t="n">
         <v>129</v>
@@ -1495,7 +1495,7 @@
         <v>177</v>
       </c>
       <c r="M23" t="n">
-        <v>1.9323</v>
+        <v>2.01</v>
       </c>
       <c r="N23" t="n">
         <v>306</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.8966</v>
+        <v>1.9204</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0264</v>
+        <v>1.0393</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3448</v>
+        <v>0.3212</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8966</v>
+        <v>1.9204</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8131</v>
+        <v>2.4139</v>
       </c>
       <c r="G24" t="n">
-        <v>1.0835</v>
+        <v>-0.4935</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8131</v>
+        <v>2.4139</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8131</v>
+        <v>2.4139</v>
       </c>
       <c r="J24" t="n">
-        <v>1.0835</v>
+        <v>-0.4935</v>
       </c>
       <c r="K24" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="L24" t="n">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="M24" t="n">
-        <v>1.8966</v>
+        <v>1.9204</v>
       </c>
       <c r="N24" t="n">
-        <v>303</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.888</v>
+        <v>1.8966</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0218</v>
+        <v>1.0264</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3413</v>
+        <v>0.3117</v>
       </c>
       <c r="E25" t="n">
-        <v>1.888</v>
+        <v>1.8966</v>
       </c>
       <c r="F25" t="n">
-        <v>2.3815</v>
+        <v>0.8131</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4935</v>
+        <v>1.0835</v>
       </c>
       <c r="H25" t="n">
-        <v>2.3815</v>
+        <v>0.8131</v>
       </c>
       <c r="I25" t="n">
-        <v>2.3815</v>
+        <v>0.8131</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4935</v>
+        <v>1.0835</v>
       </c>
       <c r="K25" t="n">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="L25" t="n">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="M25" t="n">
-        <v>1.888</v>
+        <v>1.8966</v>
       </c>
       <c r="N25" t="n">
-        <v>205</v>
+        <v>303</v>
       </c>
     </row>
     <row r="26">
@@ -1606,7 +1606,7 @@
         <v>1.0031</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3274</v>
+        <v>0.2945</v>
       </c>
       <c r="E26" t="n">
         <v>1.8535</v>
@@ -1642,231 +1642,231 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Woro2k</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.7764</v>
+        <v>1.7812</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9614</v>
+        <v>0.964</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2963</v>
+        <v>0.2657</v>
       </c>
       <c r="E27" t="n">
-        <v>1.7764</v>
+        <v>1.7812</v>
       </c>
       <c r="F27" t="n">
-        <v>1.9795</v>
+        <v>1.4896</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.2031</v>
+        <v>0.2916</v>
       </c>
       <c r="H27" t="n">
-        <v>1.9795</v>
+        <v>1.4896</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9795</v>
+        <v>1.4896</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.2031</v>
+        <v>0.2916</v>
       </c>
       <c r="K27" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="L27" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="M27" t="n">
-        <v>1.7764</v>
+        <v>1.7812</v>
       </c>
       <c r="N27" t="n">
-        <v>205</v>
+        <v>265</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>juanflatroo</t>
+          <t>Woro2k</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.6826</v>
+        <v>1.7764</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9106</v>
+        <v>0.9614</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2584</v>
+        <v>0.2638</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6826</v>
+        <v>1.7764</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6826</v>
+        <v>1.9795</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.2031</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6826</v>
+        <v>1.9795</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6826</v>
+        <v>1.9795</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.2031</v>
       </c>
       <c r="K28" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M28" t="n">
-        <v>1.6826</v>
+        <v>1.7764</v>
       </c>
       <c r="N28" t="n">
-        <v>161</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.656</v>
+        <v>1.7599</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8962</v>
+        <v>0.9524</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2476</v>
+        <v>0.2572</v>
       </c>
       <c r="E29" t="n">
-        <v>1.656</v>
+        <v>1.7599</v>
       </c>
       <c r="F29" t="n">
-        <v>1.656</v>
+        <v>2.3603</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.6004</v>
       </c>
       <c r="H29" t="n">
-        <v>1.656</v>
+        <v>2.3603</v>
       </c>
       <c r="I29" t="n">
-        <v>1.656</v>
+        <v>2.3801</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.6004</v>
       </c>
       <c r="K29" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M29" t="n">
-        <v>1.656</v>
+        <v>1.7797</v>
       </c>
       <c r="N29" t="n">
-        <v>196</v>
+        <v>245</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.6425</v>
+        <v>1.7512</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8889</v>
+        <v>0.9477</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2422</v>
+        <v>0.2538</v>
       </c>
       <c r="E30" t="n">
-        <v>1.6425</v>
+        <v>1.7512</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8046</v>
+        <v>1.7512</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8379</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8046</v>
+        <v>1.7512</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8046</v>
+        <v>1.7512</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8379</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="L30" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.6425</v>
+        <v>1.7512</v>
       </c>
       <c r="N30" t="n">
-        <v>292</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>juanflatroo</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.6199</v>
+        <v>1.7307</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8767</v>
+        <v>0.9366</v>
       </c>
       <c r="D31" t="n">
-        <v>0.233</v>
+        <v>0.2456</v>
       </c>
       <c r="E31" t="n">
-        <v>1.6199</v>
+        <v>1.7307</v>
       </c>
       <c r="F31" t="n">
-        <v>2.2203</v>
+        <v>1.7307</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.6004</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.2203</v>
+        <v>1.7307</v>
       </c>
       <c r="I31" t="n">
-        <v>2.2307</v>
+        <v>1.7307</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.6004</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="L31" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.6303</v>
+        <v>1.7307</v>
       </c>
       <c r="N31" t="n">
-        <v>245</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.5886</v>
+        <v>1.6854</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8597</v>
+        <v>0.9121</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2204</v>
+        <v>0.2276</v>
       </c>
       <c r="E32" t="n">
-        <v>1.5886</v>
+        <v>1.6854</v>
       </c>
       <c r="F32" t="n">
-        <v>1.5886</v>
+        <v>1.6854</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.5886</v>
+        <v>1.6854</v>
       </c>
       <c r="I32" t="n">
-        <v>1.5886</v>
+        <v>1.6854</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.5886</v>
+        <v>1.6854</v>
       </c>
       <c r="N32" t="n">
         <v>212</v>
@@ -1918,32 +1918,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.5725</v>
+        <v>1.656</v>
       </c>
       <c r="C33" t="n">
-        <v>0.851</v>
+        <v>0.8962</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2139</v>
+        <v>0.2158</v>
       </c>
       <c r="E33" t="n">
-        <v>1.5725</v>
+        <v>1.656</v>
       </c>
       <c r="F33" t="n">
-        <v>1.5725</v>
+        <v>1.656</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.5725</v>
+        <v>1.656</v>
       </c>
       <c r="I33" t="n">
-        <v>1.5725</v>
+        <v>1.656</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.5725</v>
+        <v>1.656</v>
       </c>
       <c r="N33" t="n">
         <v>196</v>
@@ -1964,308 +1964,308 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.5077</v>
+        <v>1.6425</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8889</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1877</v>
+        <v>0.2105</v>
       </c>
       <c r="E34" t="n">
-        <v>1.5077</v>
+        <v>1.6425</v>
       </c>
       <c r="F34" t="n">
-        <v>1.2161</v>
+        <v>0.8046</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2916</v>
+        <v>0.8379</v>
       </c>
       <c r="H34" t="n">
-        <v>1.2161</v>
+        <v>0.8046</v>
       </c>
       <c r="I34" t="n">
-        <v>1.2161</v>
+        <v>0.8046</v>
       </c>
       <c r="J34" t="n">
-        <v>0.2916</v>
+        <v>0.8379</v>
       </c>
       <c r="K34" t="n">
-        <v>210</v>
+        <v>131</v>
       </c>
       <c r="L34" t="n">
-        <v>55</v>
+        <v>161</v>
       </c>
       <c r="M34" t="n">
-        <v>1.5077</v>
+        <v>1.6425</v>
       </c>
       <c r="N34" t="n">
-        <v>265</v>
+        <v>292</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.4814</v>
+        <v>1.5801</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8017</v>
+        <v>0.8551</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1771</v>
+        <v>0.1856</v>
       </c>
       <c r="E35" t="n">
-        <v>1.4814</v>
+        <v>1.5801</v>
       </c>
       <c r="F35" t="n">
-        <v>1.4814</v>
+        <v>1.5801</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.4814</v>
+        <v>1.5801</v>
       </c>
       <c r="I35" t="n">
-        <v>1.4814</v>
+        <v>1.5801</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>126</v>
+        <v>196</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.4814</v>
+        <v>1.5801</v>
       </c>
       <c r="N35" t="n">
-        <v>126</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>gxx-</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.4782</v>
+        <v>1.5725</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8</v>
+        <v>0.851</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1758</v>
+        <v>0.1826</v>
       </c>
       <c r="E36" t="n">
-        <v>1.4782</v>
+        <v>1.5725</v>
       </c>
       <c r="F36" t="n">
-        <v>1.4782</v>
+        <v>1.5725</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.4782</v>
+        <v>1.5725</v>
       </c>
       <c r="I36" t="n">
-        <v>1.4782</v>
+        <v>1.5725</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.4782</v>
+        <v>1.5725</v>
       </c>
       <c r="N36" t="n">
-        <v>161</v>
+        <v>196</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.4153</v>
+        <v>1.5425</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7659</v>
+        <v>0.8348</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1504</v>
+        <v>0.1706</v>
       </c>
       <c r="E37" t="n">
-        <v>1.4153</v>
+        <v>1.5425</v>
       </c>
       <c r="F37" t="n">
-        <v>1.4153</v>
+        <v>1.5425</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.4153</v>
+        <v>1.5425</v>
       </c>
       <c r="I37" t="n">
-        <v>1.4153</v>
+        <v>1.5425</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.4153</v>
+        <v>1.5425</v>
       </c>
       <c r="N37" t="n">
-        <v>196</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>gxx-</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.3077</v>
+        <v>1.4782</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7077</v>
+        <v>0.8</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1069</v>
+        <v>0.145</v>
       </c>
       <c r="E38" t="n">
-        <v>1.3077</v>
+        <v>1.4782</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3077</v>
+        <v>1.4782</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.3077</v>
+        <v>1.4782</v>
       </c>
       <c r="I38" t="n">
-        <v>1.3077</v>
+        <v>1.4782</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>196</v>
+        <v>161</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.3077</v>
+        <v>1.4782</v>
       </c>
       <c r="N38" t="n">
-        <v>196</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DemQQ</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.0739</v>
+        <v>1.4153</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5812</v>
+        <v>0.7659</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0125</v>
+        <v>0.1199</v>
       </c>
       <c r="E39" t="n">
-        <v>1.0739</v>
+        <v>1.4153</v>
       </c>
       <c r="F39" t="n">
-        <v>1.1619</v>
+        <v>1.4153</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.1619</v>
+        <v>1.4153</v>
       </c>
       <c r="I39" t="n">
-        <v>1.1619</v>
+        <v>1.4153</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="L39" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.0739</v>
+        <v>1.4153</v>
       </c>
       <c r="N39" t="n">
-        <v>205</v>
+        <v>196</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.0371</v>
+        <v>1.3077</v>
       </c>
       <c r="C40" t="n">
-        <v>0.5613</v>
+        <v>0.7077</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0024</v>
+        <v>0.0771</v>
       </c>
       <c r="E40" t="n">
-        <v>1.0371</v>
+        <v>1.3077</v>
       </c>
       <c r="F40" t="n">
-        <v>1.0371</v>
+        <v>1.3077</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.0371</v>
+        <v>1.3077</v>
       </c>
       <c r="I40" t="n">
-        <v>1.0371</v>
+        <v>1.3077</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.0371</v>
+        <v>1.3077</v>
       </c>
       <c r="N40" t="n">
         <v>196</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.98</v>
+        <v>1.2154</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5304</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0255</v>
+        <v>0.0403</v>
       </c>
       <c r="E41" t="n">
-        <v>0.98</v>
+        <v>1.2154</v>
       </c>
       <c r="F41" t="n">
-        <v>0.98</v>
+        <v>1.2154</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.98</v>
+        <v>1.2154</v>
       </c>
       <c r="I41" t="n">
-        <v>0.98</v>
+        <v>1.2154</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.98</v>
+        <v>1.2154</v>
       </c>
       <c r="N41" t="n">
         <v>212</v>
@@ -2332,47 +2332,47 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>DemQQ</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9796</v>
+        <v>1.0739</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5302</v>
+        <v>0.5812</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0256</v>
+        <v>-0.0161</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9796</v>
+        <v>1.0739</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9796</v>
+        <v>1.1619</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9796</v>
+        <v>1.1619</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9796</v>
+        <v>1.1619</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>212</v>
+        <v>160</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M42" t="n">
-        <v>0.9796</v>
+        <v>1.0739</v>
       </c>
       <c r="N42" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.87</v>
+        <v>1.0116</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4708</v>
+        <v>0.5475</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0699</v>
+        <v>-0.0409</v>
       </c>
       <c r="E43" t="n">
-        <v>0.87</v>
+        <v>1.0116</v>
       </c>
       <c r="F43" t="n">
-        <v>1.8229</v>
+        <v>1.9645</v>
       </c>
       <c r="G43" t="n">
         <v>-0.9529</v>
       </c>
       <c r="H43" t="n">
-        <v>1.8229</v>
+        <v>1.9645</v>
       </c>
       <c r="I43" t="n">
-        <v>1.8229</v>
+        <v>1.9645</v>
       </c>
       <c r="J43" t="n">
         <v>-0.9529</v>
@@ -2415,7 +2415,7 @@
         <v>45</v>
       </c>
       <c r="M43" t="n">
-        <v>0.87</v>
+        <v>1.0116</v>
       </c>
       <c r="N43" t="n">
         <v>205</v>
@@ -2424,308 +2424,308 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8516</v>
+        <v>0.8868</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4609</v>
+        <v>0.4799</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.0906</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8516</v>
+        <v>0.8868</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.665</v>
+        <v>0.8868</v>
       </c>
       <c r="G44" t="n">
-        <v>1.5166</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.665</v>
+        <v>0.8868</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.665</v>
+        <v>0.8868</v>
       </c>
       <c r="J44" t="n">
-        <v>1.5166</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>113</v>
+        <v>212</v>
       </c>
       <c r="L44" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8515999999999999</v>
+        <v>0.8868</v>
       </c>
       <c r="N44" t="n">
-        <v>277</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8254</v>
+        <v>0.8669</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4467</v>
+        <v>0.4692</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.0985</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8254</v>
+        <v>0.8669</v>
       </c>
       <c r="F45" t="n">
-        <v>1.2346</v>
+        <v>0.8576</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.4092</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>1.2346</v>
+        <v>0.8576</v>
       </c>
       <c r="I45" t="n">
-        <v>1.2461</v>
+        <v>0.8576</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.4092</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>277</v>
+        <v>131</v>
       </c>
       <c r="L45" t="n">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="M45" t="n">
-        <v>0.8369</v>
+        <v>0.8669</v>
       </c>
       <c r="N45" t="n">
-        <v>357</v>
+        <v>292</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.62</v>
+        <v>0.8516</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3355</v>
+        <v>0.4609</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1709</v>
+        <v>-0.1046</v>
       </c>
       <c r="E46" t="n">
-        <v>0.62</v>
+        <v>0.8516</v>
       </c>
       <c r="F46" t="n">
-        <v>0.62</v>
+        <v>-0.665</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1.5166</v>
       </c>
       <c r="H46" t="n">
-        <v>0.62</v>
+        <v>-0.665</v>
       </c>
       <c r="I46" t="n">
-        <v>0.62</v>
+        <v>-0.665</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1.5166</v>
       </c>
       <c r="K46" t="n">
-        <v>196</v>
+        <v>113</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="M46" t="n">
-        <v>0.62</v>
+        <v>0.8515999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>196</v>
+        <v>277</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6119</v>
+        <v>0.8162</v>
       </c>
       <c r="C47" t="n">
-        <v>0.3312</v>
+        <v>0.4417</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1742</v>
+        <v>-0.1187</v>
       </c>
       <c r="E47" t="n">
-        <v>0.6119</v>
+        <v>0.8162</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6026</v>
+        <v>1.2254</v>
       </c>
       <c r="G47" t="n">
-        <v>0.009299999999999999</v>
+        <v>-0.4092</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6026</v>
+        <v>1.2254</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6026</v>
+        <v>1.2461</v>
       </c>
       <c r="J47" t="n">
-        <v>0.009299999999999999</v>
+        <v>-0.4092</v>
       </c>
       <c r="K47" t="n">
-        <v>131</v>
+        <v>277</v>
       </c>
       <c r="L47" t="n">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="M47" t="n">
-        <v>0.6119</v>
+        <v>0.8369</v>
       </c>
       <c r="N47" t="n">
-        <v>292</v>
+        <v>357</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>nicoodoz</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5397</v>
+        <v>0.62</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2921</v>
+        <v>0.3355</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2033</v>
+        <v>-0.1969</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5397</v>
+        <v>0.62</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5397</v>
+        <v>0.62</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.5397</v>
+        <v>0.62</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5397</v>
+        <v>0.62</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>253</v>
+        <v>196</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.5397</v>
+        <v>0.62</v>
       </c>
       <c r="N48" t="n">
-        <v>253</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5109</v>
+        <v>0.5648</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2765</v>
+        <v>0.3057</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.215</v>
+        <v>-0.2189</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5109</v>
+        <v>0.5648</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5109</v>
+        <v>0.5648</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.5109</v>
+        <v>0.5648</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5109</v>
+        <v>0.5648</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>212</v>
+        <v>253</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.5109</v>
+        <v>0.5648</v>
       </c>
       <c r="N49" t="n">
-        <v>212</v>
+        <v>253</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>nicoodoz</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4503</v>
+        <v>0.5397</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2437</v>
+        <v>0.2921</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2395</v>
+        <v>-0.2289</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4503</v>
+        <v>0.5397</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4503</v>
+        <v>0.5397</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4503</v>
+        <v>0.5397</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4503</v>
+        <v>0.5397</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.4503</v>
+        <v>0.5397</v>
       </c>
       <c r="N50" t="n">
         <v>253</v>
@@ -2746,599 +2746,599 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.3831</v>
+        <v>0.4954</v>
       </c>
       <c r="C51" t="n">
-        <v>0.2073</v>
+        <v>0.2681</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.2666</v>
+        <v>-0.2465</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3831</v>
+        <v>0.4954</v>
       </c>
       <c r="F51" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.0476</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.1789</v>
+        <v>-0.5522</v>
       </c>
       <c r="H51" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.0476</v>
       </c>
       <c r="I51" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.0564</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.1789</v>
+        <v>-0.5522</v>
       </c>
       <c r="K51" t="n">
-        <v>131</v>
+        <v>192</v>
       </c>
       <c r="L51" t="n">
-        <v>161</v>
+        <v>53</v>
       </c>
       <c r="M51" t="n">
-        <v>0.3831000000000001</v>
+        <v>0.5042</v>
       </c>
       <c r="N51" t="n">
-        <v>292</v>
+        <v>245</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3768</v>
+        <v>0.4607</v>
       </c>
       <c r="C52" t="n">
-        <v>0.2039</v>
+        <v>0.2493</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2691</v>
+        <v>-0.2604</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3768</v>
+        <v>0.4607</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7674</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.3906</v>
+        <v>-0.1789</v>
       </c>
       <c r="H52" t="n">
-        <v>0.7674</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7746</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.3906</v>
+        <v>-0.1789</v>
       </c>
       <c r="K52" t="n">
-        <v>277</v>
+        <v>131</v>
       </c>
       <c r="L52" t="n">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="M52" t="n">
-        <v>0.384</v>
+        <v>0.4606999999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>357</v>
+        <v>292</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.1348</v>
+        <v>0.3711</v>
       </c>
       <c r="C53" t="n">
-        <v>0.073</v>
+        <v>0.2008</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3669</v>
+        <v>-0.2961</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1348</v>
+        <v>0.3711</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1348</v>
+        <v>0.7617</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-0.3906</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1348</v>
+        <v>0.7617</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1348</v>
+        <v>0.7746</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-0.3906</v>
       </c>
       <c r="K53" t="n">
-        <v>94</v>
+        <v>277</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1348</v>
+        <v>0.384</v>
       </c>
       <c r="N53" t="n">
-        <v>94</v>
+        <v>357</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Goofy</t>
+          <t>dycha</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.122</v>
+        <v>0.1462</v>
       </c>
       <c r="C54" t="n">
-        <v>0.066</v>
+        <v>0.0791</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.3721</v>
+        <v>-0.3857</v>
       </c>
       <c r="E54" t="n">
-        <v>0.122</v>
+        <v>0.1462</v>
       </c>
       <c r="F54" t="n">
-        <v>0.122</v>
+        <v>0.1462</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.122</v>
+        <v>0.1462</v>
       </c>
       <c r="I54" t="n">
-        <v>0.122</v>
+        <v>0.1462</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.122</v>
+        <v>0.1462</v>
       </c>
       <c r="N54" t="n">
-        <v>104</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Keoz</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.104</v>
+        <v>0.1348</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0563</v>
+        <v>0.073</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.3793</v>
+        <v>-0.3902</v>
       </c>
       <c r="E55" t="n">
-        <v>0.104</v>
+        <v>0.1348</v>
       </c>
       <c r="F55" t="n">
-        <v>0.6621</v>
+        <v>0.1348</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.5581</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.6621</v>
+        <v>0.1348</v>
       </c>
       <c r="I55" t="n">
-        <v>0.6621</v>
+        <v>0.1348</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.5581</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="L55" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.104</v>
+        <v>0.1348</v>
       </c>
       <c r="N55" t="n">
-        <v>306</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Goofy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.122</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0458</v>
+        <v>0.066</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.3872</v>
+        <v>-0.3953</v>
       </c>
       <c r="E56" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.122</v>
       </c>
       <c r="F56" t="n">
-        <v>0.6368</v>
+        <v>0.122</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.5522</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.6368</v>
+        <v>0.122</v>
       </c>
       <c r="I56" t="n">
-        <v>0.6397</v>
+        <v>0.122</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.5522</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>192</v>
+        <v>104</v>
       </c>
       <c r="L56" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.08750000000000002</v>
+        <v>0.122</v>
       </c>
       <c r="N56" t="n">
-        <v>245</v>
+        <v>104</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>rigoN</t>
+          <t>Keoz</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.0371</v>
+        <v>0.104</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0201</v>
+        <v>0.0563</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4064</v>
+        <v>-0.4025</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0371</v>
+        <v>0.104</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0371</v>
+        <v>0.6621</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>-0.5581</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0371</v>
+        <v>0.6621</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0371</v>
+        <v>0.6621</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>-0.5581</v>
       </c>
       <c r="K57" t="n">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="M57" t="n">
-        <v>0.0371</v>
+        <v>0.104</v>
       </c>
       <c r="N57" t="n">
-        <v>161</v>
+        <v>306</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>dycha</t>
+          <t>rigoN</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.0336</v>
+        <v>0.0371</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0182</v>
+        <v>0.0201</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4078</v>
+        <v>-0.4291</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0336</v>
+        <v>0.0371</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0336</v>
+        <v>0.0371</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0336</v>
+        <v>0.0371</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0336</v>
+        <v>0.0371</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.0336</v>
+        <v>0.0371</v>
       </c>
       <c r="N58" t="n">
-        <v>126</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SENER1</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.4078</v>
+        <v>-0.34</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2207</v>
+        <v>-0.184</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5861</v>
+        <v>-0.5794</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.4078</v>
+        <v>-0.34</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.4078</v>
+        <v>-0.34</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.4078</v>
+        <v>-0.34</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4078</v>
+        <v>-0.34</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.4078</v>
+        <v>-0.34</v>
       </c>
       <c r="N59" t="n">
-        <v>161</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>SENER1</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.5027</v>
+        <v>-0.4078</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2721</v>
+        <v>-0.2207</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6244</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.5027</v>
+        <v>-0.4078</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.5027</v>
+        <v>-0.4078</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.5027</v>
+        <v>-0.4078</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5027</v>
+        <v>-0.4078</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.5027</v>
+        <v>-0.4078</v>
       </c>
       <c r="N60" t="n">
-        <v>126</v>
+        <v>161</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.5834</v>
+        <v>-0.5027</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.3157</v>
+        <v>-0.2721</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.657</v>
+        <v>-0.6442</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5834</v>
+        <v>-0.5027</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.5834</v>
+        <v>-0.5027</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.5834</v>
+        <v>-0.5027</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5834</v>
+        <v>-0.5027</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.5834</v>
+        <v>-0.5027</v>
       </c>
       <c r="N61" t="n">
-        <v>94</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>hades</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.6465</v>
+        <v>-0.5556</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.3499</v>
+        <v>-0.3007</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6825</v>
+        <v>-0.6653</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.6465</v>
+        <v>-0.5556</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.6465</v>
+        <v>-0.5556</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.6465</v>
+        <v>-0.5556</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.6465</v>
+        <v>-0.5556</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.6465</v>
+        <v>-0.5556</v>
       </c>
       <c r="N62" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>hades</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.9032</v>
+        <v>-0.6465</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.4888</v>
+        <v>-0.3499</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7862</v>
+        <v>-0.7015</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.9032</v>
+        <v>-0.6465</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.9032</v>
+        <v>-0.6465</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.9032</v>
+        <v>-0.6465</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.9032</v>
+        <v>-0.6465</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.9032</v>
+        <v>-0.6465</v>
       </c>
       <c r="N63" t="n">
-        <v>126</v>
+        <v>104</v>
       </c>
     </row>
     <row r="64">
@@ -3354,7 +3354,7 @@
         <v>-0.4901</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7872</v>
+        <v>-0.8047</v>
       </c>
       <c r="E64" t="n">
         <v>-0.9056</v>
@@ -3400,7 +3400,7 @@
         <v>-0.5195</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8092</v>
+        <v>-0.8264</v>
       </c>
       <c r="E65" t="n">
         <v>-0.96</v>
@@ -3446,7 +3446,7 @@
         <v>-0.546</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8289</v>
+        <v>-0.8459</v>
       </c>
       <c r="E66" t="n">
         <v>-1.0089</v>
@@ -3492,7 +3492,7 @@
         <v>-0.556</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8364</v>
+        <v>-0.8532</v>
       </c>
       <c r="E67" t="n">
         <v>-1.0273</v>
@@ -3528,262 +3528,262 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.1552</v>
+        <v>-1.0456</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.6252</v>
+        <v>-0.5659</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.888</v>
+        <v>-0.8605</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.1552</v>
+        <v>-1.0456</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.1552</v>
+        <v>0.2561</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>-1.3017</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.1552</v>
+        <v>0.2561</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1552</v>
+        <v>0.2561</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>-1.3017</v>
       </c>
       <c r="K68" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.1552</v>
+        <v>-1.0456</v>
       </c>
       <c r="N68" t="n">
-        <v>196</v>
+        <v>303</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.2136</v>
+        <v>-1.1552</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.6252</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9116</v>
+        <v>-0.9041</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.2136</v>
+        <v>-1.1552</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.2136</v>
+        <v>-1.1552</v>
       </c>
       <c r="G69" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.2136</v>
+        <v>-1.1552</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2136</v>
+        <v>-1.1552</v>
       </c>
       <c r="J69" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="L69" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.2136</v>
+        <v>-1.1552</v>
       </c>
       <c r="N69" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.2463</v>
+        <v>-1.2136</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.6745</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9248</v>
+        <v>-0.9274</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.2463</v>
+        <v>-1.2136</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.4428</v>
+        <v>-0.2136</v>
       </c>
       <c r="G70" t="n">
-        <v>0.1965</v>
+        <v>-1</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.4428</v>
+        <v>-0.2136</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.4428</v>
+        <v>-0.2136</v>
       </c>
       <c r="J70" t="n">
-        <v>0.1965</v>
+        <v>-1</v>
       </c>
       <c r="K70" t="n">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="L70" t="n">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.2463</v>
+        <v>-1.2136</v>
       </c>
       <c r="N70" t="n">
-        <v>303</v>
+        <v>265</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FASHR</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.3903</v>
+        <v>-1.2463</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.7524</v>
+        <v>-0.6745</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.983</v>
+        <v>-0.9404</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.3903</v>
+        <v>-1.2463</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.3903</v>
+        <v>-1.4428</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>0.1965</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.3903</v>
+        <v>-1.4428</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.3903</v>
+        <v>-1.4428</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>0.1965</v>
       </c>
       <c r="K71" t="n">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.3903</v>
+        <v>-1.2463</v>
       </c>
       <c r="N71" t="n">
-        <v>253</v>
+        <v>303</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KEi</t>
+          <t>FASHR</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.4252</v>
+        <v>-1.3903</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.7713</v>
+        <v>-0.7524</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9971</v>
+        <v>-0.9978</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.4252</v>
+        <v>-1.3903</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.4252</v>
+        <v>-1.3903</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.4252</v>
+        <v>-1.3903</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.4252</v>
+        <v>-1.3903</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>104</v>
+        <v>253</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.4252</v>
+        <v>-1.3903</v>
       </c>
       <c r="N72" t="n">
-        <v>104</v>
+        <v>253</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>mynio</t>
+          <t>KEi</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.5409</v>
+        <v>-1.4252</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.8339</v>
+        <v>-0.7713</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0439</v>
+        <v>-1.0117</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.5409</v>
+        <v>-1.4252</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.5409</v>
+        <v>-1.4252</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.5409</v>
+        <v>-1.4252</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.5409</v>
+        <v>-1.4252</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.5409</v>
+        <v>-1.4252</v>
       </c>
       <c r="N73" t="n">
         <v>104</v>
@@ -3804,47 +3804,47 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>mynio</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.6207</v>
+        <v>-1.5409</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.8771</v>
+        <v>-0.8339</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0761</v>
+        <v>-1.0578</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.6207</v>
+        <v>-1.5409</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.319</v>
+        <v>-1.5409</v>
       </c>
       <c r="G74" t="n">
-        <v>-1.3017</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.319</v>
+        <v>-1.5409</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.319</v>
+        <v>-1.5409</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.3017</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>192</v>
+        <v>104</v>
       </c>
       <c r="L74" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.6207</v>
+        <v>-1.5409</v>
       </c>
       <c r="N74" t="n">
-        <v>303</v>
+        <v>104</v>
       </c>
     </row>
     <row r="75">
@@ -3860,7 +3860,7 @@
         <v>-0.9731</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1478</v>
+        <v>-1.1603</v>
       </c>
       <c r="E75" t="n">
         <v>-1.7981</v>
@@ -3906,7 +3906,7 @@
         <v>-1.0293</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1897</v>
+        <v>-1.2017</v>
       </c>
       <c r="E76" t="n">
         <v>-1.902</v>
@@ -3952,7 +3952,7 @@
         <v>-1.0329</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1924</v>
+        <v>-1.2043</v>
       </c>
       <c r="E77" t="n">
         <v>-1.9086</v>
@@ -3998,7 +3998,7 @@
         <v>-1.1007</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.243</v>
+        <v>-1.2542</v>
       </c>
       <c r="E78" t="n">
         <v>-2.0339</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.0601</v>
+        <v>-2.0523</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.1149</v>
+        <v>-1.1107</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2536</v>
+        <v>-1.2615</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.0601</v>
+        <v>-2.0523</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.071</v>
+        <v>-2.0632</v>
       </c>
       <c r="G79" t="n">
         <v>0.0109</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.071</v>
+        <v>-2.0632</v>
       </c>
       <c r="I79" t="n">
         <v>-2.0806</v>
@@ -4090,7 +4090,7 @@
         <v>-1.856</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.8068</v>
+        <v>-1.8102</v>
       </c>
       <c r="E80" t="n">
         <v>-3.4295</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-4.4975</v>
+        <v>-4.4714</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.434</v>
+        <v>-2.4199</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.2383</v>
+        <v>-2.2253</v>
       </c>
       <c r="E81" t="n">
-        <v>-4.4975</v>
+        <v>-4.4714</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.4975</v>
+        <v>-3.4714</v>
       </c>
       <c r="G81" t="n">
         <v>-1</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.4975</v>
+        <v>-3.4714</v>
       </c>
       <c r="I81" t="n">
         <v>-3.5301</v>
